--- a/data/gravel/Nordest Sardinha 2 2025.xlsx
+++ b/data/gravel/Nordest Sardinha 2 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88E3E2CB-42C1-0E49-8C2B-BEA54318893B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{432DB161-A2BB-5E40-BB79-C90F6965F945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19580" yWindow="-23040" windowWidth="25220" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12040" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="109">
   <si>
     <t>brand</t>
   </si>
@@ -378,6 +378,9 @@
   </si>
   <si>
     <t>steel</t>
+  </si>
+  <si>
+    <t>https://nordestcycles.com/wp-content/uploads/2020/03/Kit-Sardinha-2-B-01.png</t>
   </si>
 </sst>
 </file>
@@ -816,6 +819,11 @@
         <v>106</v>
       </c>
     </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B6" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>5</v>

--- a/data/gravel/Nordest Sardinha 2 2025.xlsx
+++ b/data/gravel/Nordest Sardinha 2 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{432DB161-A2BB-5E40-BB79-C90F6965F945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5C5B436-DA9E-C440-A4AC-642F9D44F686}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12040" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="111">
   <si>
     <t>brand</t>
   </si>
@@ -381,6 +381,12 @@
   </si>
   <si>
     <t>https://nordestcycles.com/wp-content/uploads/2020/03/Kit-Sardinha-2-B-01.png</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Madrid, Spain</t>
   </si>
 </sst>
 </file>
@@ -772,7 +778,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K70"/>
+  <dimension ref="A1:K71"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -1630,6 +1636,14 @@
         <v>89</v>
       </c>
     </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Nordest Sardinha 2 2025.xlsx
+++ b/data/gravel/Nordest Sardinha 2 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5C5B436-DA9E-C440-A4AC-642F9D44F686}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0380412-FCA6-0641-9AAE-7FB544BB5737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="112">
   <si>
     <t>brand</t>
   </si>
@@ -387,6 +387,9 @@
   </si>
   <si>
     <t>Madrid, Spain</t>
+  </si>
+  <si>
+    <t>internal</t>
   </si>
 </sst>
 </file>
@@ -1543,6 +1546,9 @@
       <c r="A57" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="B57" s="1" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">

--- a/data/gravel/Nordest Sardinha 2 2025.xlsx
+++ b/data/gravel/Nordest Sardinha 2 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0380412-FCA6-0641-9AAE-7FB544BB5737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A526396-F458-3148-89D2-37073A588FEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="118">
   <si>
     <t>brand</t>
   </si>
@@ -390,6 +390,24 @@
   </si>
   <si>
     <t>internal</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -781,7 +799,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K71"/>
+  <dimension ref="A1:K77"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -1488,165 +1506,195 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>43</v>
+        <v>113</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B49" s="1">
-        <v>31.6</v>
+        <v>114</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>45</v>
+        <v>115</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>46</v>
+        <v>116</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>47</v>
+        <v>117</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
+      </c>
+      <c r="B55" s="1">
+        <v>31.6</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>111</v>
+        <v>46</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B60" s="1">
-        <v>2</v>
+        <v>49</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B61" s="1">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B62" s="1">
-        <v>1</v>
+        <v>51</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B63" s="1">
-        <v>3</v>
+        <v>52</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>71</v>
+        <v>55</v>
+      </c>
+      <c r="B66" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B67" s="1">
-        <v>949</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
+      </c>
+      <c r="B68" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
+      </c>
+      <c r="B69" s="1">
+        <v>3</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B73" s="1">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="B77" s="1" t="s">
         <v>110</v>
       </c>
     </row>

--- a/data/gravel/Nordest Sardinha 2 2025.xlsx
+++ b/data/gravel/Nordest Sardinha 2 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A526396-F458-3148-89D2-37073A588FEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A55DF8FD-5AE3-814C-B523-476F73AEC516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4920" yWindow="1060" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="120">
   <si>
     <t>brand</t>
   </si>
@@ -245,9 +245,6 @@
     <t>fork</t>
   </si>
   <si>
-    <t>rigid</t>
-  </si>
-  <si>
     <t>yes</t>
   </si>
   <si>
@@ -291,9 +288,6 @@
   </si>
   <si>
     <t>Nordest</t>
-  </si>
-  <si>
-    <t>a8:e30</t>
   </si>
   <si>
     <t>Stem</t>
@@ -408,6 +402,18 @@
   </si>
   <si>
     <t>fork_material</t>
+  </si>
+  <si>
+    <t>fork_travel</t>
+  </si>
+  <si>
+    <t>fork_sag</t>
+  </si>
+  <si>
+    <t>a8:e32</t>
+  </si>
+  <si>
+    <t>suspension</t>
   </si>
 </sst>
 </file>
@@ -799,7 +805,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K77"/>
+  <dimension ref="A1:K79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -811,7 +817,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -819,7 +825,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -843,12 +849,12 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
@@ -856,7 +862,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>86</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
@@ -864,28 +870,28 @@
         <v>6</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="E8" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="E8" s="10" t="s">
-        <v>76</v>
-      </c>
       <c r="G8" s="6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H8" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="I8" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="I8" s="6" t="s">
+      <c r="J8" t="s">
         <v>75</v>
-      </c>
-      <c r="J8" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
@@ -893,7 +899,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C9" s="3">
         <v>67</v>
@@ -905,10 +911,10 @@
         <v>67</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I9" s="8">
         <v>67</v>
@@ -925,7 +931,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C10" s="3">
         <v>120</v>
@@ -937,10 +943,10 @@
         <v>145</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I10" s="8">
         <v>120</v>
@@ -957,7 +963,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C11" s="3">
         <v>600</v>
@@ -969,10 +975,10 @@
         <v>661</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I11" s="8">
         <v>600</v>
@@ -989,7 +995,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C12" s="3">
         <v>74.5</v>
@@ -1001,10 +1007,10 @@
         <v>74</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I12" s="8">
         <v>74.5</v>
@@ -1021,7 +1027,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C13" s="3">
         <v>420</v>
@@ -1033,10 +1039,10 @@
         <v>485</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I13" s="8">
         <v>420</v>
@@ -1053,7 +1059,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C14" s="3">
         <v>430</v>
@@ -1065,10 +1071,10 @@
         <v>430</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I14" s="8">
         <v>430</v>
@@ -1085,7 +1091,7 @@
         <v>16</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C15" s="3">
         <v>435</v>
@@ -1097,10 +1103,10 @@
         <v>485</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I15" s="8">
         <v>435</v>
@@ -1117,7 +1123,7 @@
         <v>17</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C16" s="3">
         <v>599</v>
@@ -1129,10 +1135,10 @@
         <v>622</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I16" s="8">
         <v>599</v>
@@ -1149,7 +1155,7 @@
         <v>13</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C17" s="3">
         <v>60</v>
@@ -1161,10 +1167,10 @@
         <v>60</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I17" s="8">
         <v>60</v>
@@ -1181,7 +1187,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C18" s="3">
         <v>1145</v>
@@ -1193,10 +1199,10 @@
         <v>1205</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I18" s="8">
         <v>1145</v>
@@ -1213,7 +1219,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C19" s="3">
         <v>483</v>
@@ -1226,10 +1232,10 @@
       </c>
       <c r="F19" s="8"/>
       <c r="G19" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I19" s="8">
         <v>483</v>
@@ -1246,7 +1252,7 @@
         <v>22</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C20" s="3">
         <v>70</v>
@@ -1259,10 +1265,10 @@
       </c>
       <c r="F20" s="7"/>
       <c r="G20" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I20" s="5">
         <v>70</v>
@@ -1289,413 +1295,447 @@
         <v>51</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>15</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3">
+        <v>100</v>
+      </c>
+      <c r="D22" s="3">
+        <v>100</v>
+      </c>
+      <c r="E22" s="3">
+        <v>100</v>
+      </c>
+      <c r="F22" s="5"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3">
         <v>20</v>
       </c>
+      <c r="D23" s="3">
+        <v>20</v>
+      </c>
+      <c r="E23" s="3">
+        <v>20</v>
+      </c>
+      <c r="F23" s="5"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D25" s="4">
-        <v>2750</v>
-      </c>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
+        <v>20</v>
+      </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="1">
-        <v>700</v>
-      </c>
-      <c r="D26" s="1">
-        <v>700</v>
-      </c>
-      <c r="E26" s="1">
-        <v>700</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C27" s="1">
-        <v>2.6</v>
-      </c>
-      <c r="D27" s="1">
-        <v>2.6</v>
-      </c>
-      <c r="E27" s="1">
-        <v>2.6</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="D27" s="4">
+        <v>2750</v>
+      </c>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C28" s="1">
-        <v>2.6</v>
+        <v>700</v>
       </c>
       <c r="D28" s="1">
-        <v>2.6</v>
+        <v>700</v>
       </c>
       <c r="E28" s="1">
-        <v>2.6</v>
+        <v>700</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="C29" s="1">
-        <v>168</v>
+        <v>2.6</v>
       </c>
       <c r="D29" s="1">
-        <v>175</v>
+        <v>2.6</v>
       </c>
       <c r="E29" s="1">
-        <v>182</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="C30" s="1">
-        <v>178</v>
+        <v>2.6</v>
       </c>
       <c r="D30" s="1">
-        <v>185</v>
+        <v>2.6</v>
       </c>
       <c r="E30" s="1">
-        <v>193</v>
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C31" s="1">
+        <v>168</v>
+      </c>
+      <c r="D31" s="1">
+        <v>175</v>
+      </c>
+      <c r="E31" s="1">
+        <v>182</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>67</v>
+        <v>28</v>
+      </c>
+      <c r="C32" s="1">
+        <v>178</v>
+      </c>
+      <c r="D32" s="1">
+        <v>185</v>
+      </c>
+      <c r="E32" s="1">
+        <v>193</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>90</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>31</v>
+        <v>68</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="G36"/>
+        <v>88</v>
+      </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H37"/>
+        <v>69</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>33</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="G38"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B39" s="1">
-        <v>2.6</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="H39"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B40" s="1">
-        <v>3</v>
+        <v>33</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B41" s="1">
-        <v>10</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42"/>
+        <v>35</v>
+      </c>
+      <c r="B42" s="1">
+        <v>3</v>
+      </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
+      </c>
+      <c r="B43" s="1">
+        <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
+      </c>
+      <c r="B44" s="1">
+        <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="1">
-        <v>148</v>
+        <v>38</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="1">
-        <v>110</v>
+        <v>39</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>112</v>
+        <v>40</v>
+      </c>
+      <c r="B47" s="1">
+        <v>148</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>113</v>
+        <v>41</v>
+      </c>
+      <c r="B48" s="1">
+        <v>110</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>91</v>
+        <v>114</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>43</v>
+        <v>115</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B55" s="1">
-        <v>31.6</v>
+        <v>42</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
+      </c>
+      <c r="B57" s="1">
+        <v>31.6</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>111</v>
+        <v>50</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B66" s="1">
-        <v>2</v>
+        <v>53</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B67" s="1">
-        <v>1</v>
+        <v>54</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B68" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B69" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>71</v>
+        <v>57</v>
+      </c>
+      <c r="B70" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>71</v>
+        <v>58</v>
+      </c>
+      <c r="B71" s="1">
+        <v>3</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B73" s="1">
-        <v>949</v>
+        <v>60</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
+      </c>
+      <c r="B75" s="1">
+        <v>949</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>89</v>
+        <v>63</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>110</v>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
